--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2022_magallanes.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2022_magallanes.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:47</t>
+    <t xml:space="preserve">2026-10-05 02:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>357530.16</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>381045.94</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -866,7 +866,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>395756.62</v>
+        <v>395756.63</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>332189.75</v>
@@ -913,7 +913,7 @@
         <v>382346.31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -1031,7 +1031,7 @@
         <v>33</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>357874.62</v>
+        <v>357874.63</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>305187.22</v>
@@ -1064,7 +1064,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>355522.12</v>
+        <v>355522.13</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>321537.41</v>
@@ -1152,7 +1152,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>387331.62</v>
+        <v>387331.63</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>340767.66</v>
@@ -1207,7 +1207,7 @@
         <v>49</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>407596.62</v>
+        <v>407596.63</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>372099.75</v>
@@ -1287,7 +1287,7 @@
         <v>437011.31</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1529,7 +1529,7 @@
         <v>488845.59</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>503419.38</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
@@ -1614,7 +1614,7 @@
         <v>86</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>548605.62</v>
+        <v>548605.63</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>497221.19</v>
